--- a/relax_new.xlsx
+++ b/relax_new.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reference_sources" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="run_sources" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMSD_vs_expert" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMSD_sources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,8 +465,8 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -539,7 +540,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>37/40</t>
+          <t>36/40</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -558,10 +559,10 @@
         <v>44.28498391602105</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.00500748349999382</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0229</v>
+        <v>0.02340164637055943</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
     </row>
@@ -597,10 +598,10 @@
         <v>-40.87444829313423</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.0041</v>
+        <v>0.004052164062167007</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0156</v>
+        <v>0.01524915846297841</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
     </row>
@@ -617,7 +618,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>35/40</t>
+          <t>31/40</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -636,10 +637,10 @@
         <v>-47.44763814953487</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.0074</v>
+        <v>0.01487157142122967</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.0283</v>
+        <v>0.03178943351461791</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
     </row>
@@ -675,10 +676,10 @@
         <v>-78.45128968879305</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.005124782716816927</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.0154</v>
+        <v>0.01538052676919223</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
     </row>
@@ -714,10 +715,10 @@
         <v>11.47717320203735</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.005089879422948404</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0327</v>
+        <v>0.02180082108296232</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -14412,362 +14413,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR7"/>
+  <dimension ref="A1:AR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="8" customWidth="1" min="34" max="34"/>
-    <col width="8" customWidth="1" min="35" max="35"/>
-    <col width="9" customWidth="1" min="36" max="36"/>
-    <col width="8" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="8" customWidth="1" min="40" max="40"/>
-    <col width="8" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="28" max="28"/>
+    <col width="23" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="23" customWidth="1" min="31" max="31"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="21" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="23" customWidth="1" min="38" max="38"/>
+    <col width="24" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="40" max="40"/>
+    <col width="23" customWidth="1" min="41" max="41"/>
     <col width="11" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="23" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>StructureMatcher RMSD (normalized) vs expert (vasp_benchmark_old/relax). '/'=no candidate, 'no-match'=structure too different to match. vaspagent uses pv/sv/_d-pseudopotential re-runs (rxpv_*) where available (BaFeO3, BaTiO3, CaF2, Cr, FeSe, Li4Ti5O12, LiCoO2, LiFePO4, LiMn2O4, NaCl, SnSe, TiPbO3), matching the expert pseudopotentials; other systems use the original rx_* runs. Cr uses the completed rxpv_Cr rerun for energy accounting; the original RMSD entry is retained because the expert final Cr structure used to generate this sheet is not present in the current workspace. Copied from the previous workbook during the 2026-06-26 energy rebuild; RMSD values were not recomputed because pymatgen/StructureMatcher is unavailable in the default conda environment.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
-      <c r="AA1" s="1" t="n"/>
-      <c r="AB1" s="1" t="n"/>
-      <c r="AC1" s="1" t="n"/>
-      <c r="AD1" s="1" t="n"/>
-      <c r="AE1" s="1" t="n"/>
-      <c r="AF1" s="1" t="n"/>
-      <c r="AG1" s="1" t="n"/>
-      <c r="AH1" s="1" t="n"/>
-      <c r="AI1" s="1" t="n"/>
-      <c r="AJ1" s="1" t="n"/>
-      <c r="AK1" s="1" t="n"/>
-      <c r="AL1" s="1" t="n"/>
-      <c r="AM1" s="1" t="n"/>
-      <c r="AN1" s="1" t="n"/>
-      <c r="AO1" s="1" t="n"/>
-      <c r="AP1" s="1" t="n"/>
-      <c r="AQ1" s="1" t="n"/>
-      <c r="AR1" s="1" t="n"/>
+          <t>model / group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AlN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>BaFeO3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>BaTiO3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bi2Te3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CaF2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CoSb3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>FeS2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>FeSe</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Li10Ge(PS6)2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Li2S</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Li4Ti5O12</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Li7La3Zr2O12</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>LiCoO2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>LiFeAs</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>LiFePO4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>LiMn2O4</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>LiNbO3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MgB2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Nb3Sn</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>NbN</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Sb2Te3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>SnSe</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Sr2RuO4</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>TiC</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>TiPbO3</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>n_matched</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rms</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>median_rms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>model / group</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Al</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AlN</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Au</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>BaFeO3</t>
-        </is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.002183598698738427</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.006436079360461098</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.0007948385271873033</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.001911513137688005</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>BaTiO3</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Bi2Te3</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>BN</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>CaCO3</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>CaF2</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>CoSb3</t>
-        </is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.002896316071516734</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.01397739315832359</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.03782619813286203</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.001474959828770949</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.003250657663820255</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Cr</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Cu</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Fe</t>
-        </is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.0009027683345519501</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.02207081792005548</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>FeS2</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>FeSe</t>
-        </is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.01042603540841883</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Li2S</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Li4Ti5O12</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Li7La3Zr2O12</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Li10Ge(PS6)2</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>LiCoO2</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>LiFeAs</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>LiFePO4</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LiMn2O4</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>LiNbO3</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Mg</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>MgB2</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>MgO</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>NaCl</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>Nb3Sn</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>NbN</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>Ni</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>Sb2Te3</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>SiO2</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>SnSe</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>Sr2RuO4</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>TePb</t>
-        </is>
-      </c>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="inlineStr">
-        <is>
-          <t>TiC</t>
-        </is>
-      </c>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>TiPbO3</t>
-        </is>
-      </c>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>Zn</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>n_matched</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>mean_rms</t>
-        </is>
-      </c>
-      <c r="AR2" s="2" t="inlineStr">
-        <is>
-          <t>median_rms</t>
-        </is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.002889202201695547</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.01778070484166745</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0.106062202723852</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.003647524457025916</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>0.0291479398774704</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>0.04120221855144331</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>0.09860016548650738</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>0.02520866405498364</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0.005238478000981063</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>0.001047962874271256</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>0.004776488999006577</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>0.002556779272132949</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>0.00367269568234915</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.005878789845947235</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>0.001554625508547957</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>0.006893128049059416</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>0.2834066666836649</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>0.07795356886573784</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>0.007235617067140766</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>0.00915156491734501</v>
+      </c>
+      <c r="AL2" s="3" t="n">
+        <v>0.0006284199894252312</v>
+      </c>
+      <c r="AM2" s="3" t="n">
+        <v>5.564911547960893e-05</v>
+      </c>
+      <c r="AN2" s="3" t="n">
+        <v>0.001185047081731003</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>0.002533988950278988</v>
+      </c>
+      <c r="AP2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
+        <v>0.02340164637055943</v>
+      </c>
+      <c r="AR2" s="3" t="n">
+        <v>0.00500748349999382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek-V3.2</t>
+          <t>Gemini-3.1-pro</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.00218945086010734</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.0064</v>
+        <v>0.006436079360461098</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.0014</v>
+        <v>5.478212211909722e-05</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0001710886363886595</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.014</v>
+        <v>0.00289308718435707</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.0019</v>
+        <v>0.01447541379427334</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.0378</v>
+        <v>0.04040807648938955</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0012</v>
+        <v>0.0008008146310858256</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.0033</v>
+        <v>0.004052164062167007</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -14775,177 +14872,183 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>no-match</t>
-        </is>
+        <v>0.0009486960004225254</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.001464153083390257</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.009626331802052955</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.0104</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.0029</v>
+        <v>0.002560599671570589</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.0178</v>
+        <v>0.002979002635207655</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.1061</v>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
+        <v>0.01450867711196074</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>0.1073273496314046</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.004822405892536942</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0.0291</v>
-      </c>
       <c r="W3" s="3" t="n">
-        <v>0.0412</v>
+        <v>0.01975506769471053</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.01357072507847592</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.0252</v>
+        <v>0.03906814858296064</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.006848893359321939</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>0.001</v>
+        <v>0.0008044383817787275</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.0004177368194745261</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>0.0026</v>
+        <v>0.003282824004307226</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.003242380704391078</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.0059</v>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>0.0016</v>
+        <v>0.004428512457209291</v>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.02264749493946324</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.2834</v>
+        <v>0.106834438779738</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>0.078</v>
+        <v>0.07193074954481446</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.01033762656259347</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>0.0092</v>
+        <v>0.01030790234950421</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005705197960789284</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>0.0001</v>
+        <v>0.0001113262657198343</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>0.0012</v>
+        <v>0.001065732384834569</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.002777855529972708</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AQ3" s="3" t="n">
-        <v>0.0229</v>
+        <v>0.01524915846297841</v>
       </c>
       <c r="AR3" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.004052164062167007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Gemini-3.1-pro</t>
+          <t>GPT-5.2</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.003695146170641203</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.03794908910519493</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+        <v>0.01487157142122967</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.03268839892435865</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.01403336844477177</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.01848166853434164</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.07763202996618425</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.03326000343179441</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.05254916328949335</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.007370943702858846</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.0265</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="n">
+        <v>0.0080645863756102</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0.0015</v>
-      </c>
       <c r="O4" s="3" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.02031178488436479</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.003</v>
+        <v>0.04874525527425488</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0145</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>0.1073</v>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
+        <v>0.002856582700804524</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>0.0045</v>
+      <c r="T4" s="3" t="n">
+        <v>0.1070310183643938</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -14953,31 +15056,31 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.0198</v>
+        <v>0.03422207934179338</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.0136</v>
+        <v>0.05426383160370985</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.0391</v>
+        <v>0.03485105550938997</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.004955035961657632</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>0.001</v>
+        <v>0.001062571010052342</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>0.0004</v>
+        <v>0.0004041762184044434</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>0.0033</v>
+        <v>0.002619354852309142</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.003114367227437251</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.0044</v>
+        <v>0.005208558743679301</v>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
@@ -14985,77 +15088,81 @@
         </is>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.0226</v>
+        <v>0.02067745752264426</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.1068</v>
+        <v>0.2546249725939665</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="AJ4" s="3" t="n">
-        <v>0.0103</v>
+        <v>0.07796723508920651</v>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>0.0103</v>
+        <v>0.008580210575305744</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0007104329235682016</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="AN4" s="3" t="n">
-        <v>0.0011</v>
+        <v>0.0001457823188309226</v>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>0.0028</v>
+        <v>0.002524706870902941</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AQ4" s="3" t="n">
-        <v>0.0156</v>
+        <v>0.03178943351461791</v>
       </c>
       <c r="AR4" s="3" t="n">
-        <v>0.0041</v>
+        <v>0.01487157142122967</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GPT-5.2</t>
+          <t>Qwen3.5-397B</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.002174726209140115</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.0066</v>
+        <v>0.006491999669041014</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0001</v>
+        <v>0.0006543974189220024</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.014</v>
+        <v>0.0001501264636365031</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.0029</v>
+        <v>0.005078865331118045</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.0776</v>
+        <v>0.002754618340271681</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.01691640872737636</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.0333</v>
+        <v>0.04065776602926259</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.001395220923108696</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.0074</v>
+        <v>0.003680410554974086</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -15063,7 +15170,7 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.0009</v>
+        <v>0.0007490817609659112</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -15071,380 +15178,234 @@
         </is>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.0203</v>
+        <v>0.009916564645328668</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.0487</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
+        <v>0.05025519965831777</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
+      <c r="R5" s="3" t="n">
+        <v>0.003096635491590901</v>
+      </c>
       <c r="S5" s="3" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
+        <v>0.01901632038166249</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0.05716463819641743</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0.004843795482063104</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0.01738283852758784</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.02066165831263111</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>0.01356975769464243</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0.04059187529995337</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0.007150569237561343</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>0.001063408982777002</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>0.0005764371125110992</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>0.002394179396228564</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>0.003687846603783309</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.00517070010251581</v>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>0.0543</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>0.0349</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="AC5" s="3" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="AD5" s="3" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="AE5" s="3" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AF5" s="3" t="n">
-        <v>0.009900000000000001</v>
-      </c>
       <c r="AG5" s="3" t="n">
-        <v>0.0474</v>
+        <v>0.02241601623254694</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.2546</v>
+        <v>0.09289816927010713</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>0.078</v>
+        <v>0.07628345129924285</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.0406</v>
+        <v>0.009923374679300831</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>0.0086</v>
+        <v>0.0098295961029743</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0006202745787195522</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>0.0001</v>
+        <v>0.0001940706478373686</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.0654</v>
+        <v>0.001718354792327636</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.002569609534474334</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AQ5" s="3" t="n">
-        <v>0.0283</v>
+        <v>0.01538052676919223</v>
       </c>
       <c r="AR5" s="3" t="n">
-        <v>0.0074</v>
+        <v>0.005124782716816927</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Qwen3.5-397B</t>
+          <t>VASP Agent</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.005010466362264667</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.0065</v>
+        <v>0.006781066515118519</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0007433407455345569</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.0002527298345290329</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.0028</v>
+        <v>0.001636226977935028</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.0169</v>
+        <v>0.00516929248363214</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.02696700997074768</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0407</v>
+        <v>0.04060012340417907</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0014</v>
+        <v>0.001215635484737187</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
+        <v>0.002831342229241778</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.006793827931441157</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
+        <v>0.0002916568192892844</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0.001107605950592388</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.008869884269286012</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.0503</v>
+        <v>0.00296297629074598</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.1061252169227853</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.019</v>
+        <v>0.003338437969802597</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.0572</v>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
+        <v>0.01725523138912591</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0.1068396079697189</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.0048</v>
+        <v>0.003668357717612855</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.0174</v>
+        <v>0.01815159437277534</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.0207</v>
+        <v>0.01461188746495736</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.0136</v>
+        <v>0.04789841258540362</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.0406</v>
+        <v>0.03351610815199555</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.003480764433610758</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>0.0011</v>
+        <v>0.002226702117341248</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0006375832929175597</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>0.0024</v>
+        <v>0.00324451541495141</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.004783404203116778</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
+        <v>0.006427962652613512</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>0.0009001468876979925</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.0224</v>
+        <v>0.02239484384306256</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.0929</v>
+        <v>0.2601268953420929</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.07804890777312104</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.009982488182287733</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.006869786304625283</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005990842914616618</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>0.0002</v>
+        <v>0.001294122021800792</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.0017</v>
+        <v>0.007188110101954133</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.0026</v>
+        <v>0.001189486642385347</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AQ6" s="3" t="n">
-        <v>0.0154</v>
+        <v>0.02180082108296232</v>
       </c>
       <c r="AR6" s="3" t="n">
-        <v>0.0052</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>VASP Agent</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0.0406</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.4422</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0.0089</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.0173</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>0.1068</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>0.1061</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>0.0182</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0.0479</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0.0335</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="AA7" s="3" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="AC7" s="3" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="AD7" s="3" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="AE7" s="3" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="AG7" s="3" t="n">
-        <v>0.0224</v>
-      </c>
-      <c r="AH7" s="3" t="n">
-        <v>0.2601</v>
-      </c>
-      <c r="AI7" s="3" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="AJ7" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AK7" s="3" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="AL7" s="3" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="AM7" s="3" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="AN7" s="3" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="AP7" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ7" s="3" t="n">
-        <v>0.0327</v>
-      </c>
-      <c r="AR7" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.005089879422948404</v>
       </c>
     </row>
   </sheetData>
@@ -15453,6 +15414,5996 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F201"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>reference_structure</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>run_structure</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rmsd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Al/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_38/Al/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.002183598698738427</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AlN</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/AlN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_38/AlN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.006436079360461098</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Au/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_38/Au/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.0007948385271873033</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_38/BN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.001911513137688005</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>BaFeO3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaFeO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_37/BaFeO3/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BaTiO3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaTiO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_38/BaTiO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.002896316071516734</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bi2Te3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Bi2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_03_36/Bi2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.01397739315832359</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaCO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_04_02/CaCO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.03782619813286203</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CaF2</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaF2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_04_39/CaF2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.001474959828770949</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CoSb3</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CoSb3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_05_16/CoSb3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.003250657663820255</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cr/relax_cr35_reference_rerun_20260625/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_05_16/Cr/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cu/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_05_17/Cu/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0009027683345519501</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Fe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_05_53/Fe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.02207081792005548</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>FeS2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeS2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_05_30/FeS2/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>FeSe</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_05_45/FeSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.01042603540841883</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Li10Ge(PS6)2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li10Ge(PS6)2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>missing run structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Li2S</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li2S/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_06_33/Li2S/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.002889202201695547</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Li4Ti5O12</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li4Ti5O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_13_15/Li4Ti5O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.01778070484166745</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Li7La3Zr2O12</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li7La3Zr2O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_13_45/Li7La3Zr2O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.106062202723852</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>LiCoO2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiCoO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_14_21/LiCoO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.003647524457025916</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>LiFeAs</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFeAs/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_14_51/LiFeAs/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0291479398774704</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>LiFePO4</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFePO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_20_37/LiFePO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.04120221855144331</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>LiMn2O4</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiMn2O4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-20_34_21/LiMn2O4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.09860016548650738</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>LiNbO3</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiNbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_24_52/LiNbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.02520866405498364</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Mg/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_36_31/Mg/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.005238478000981063</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>MgB2</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgB2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_26_08/MgB2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.001047962874271256</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgO/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_28_18/MgO/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.004776488999006577</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NaCl/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_39_43/NaCl/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.002556779272132949</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Nb3Sn</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Nb3Sn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_46_18/Nb3Sn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.00367269568234915</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>NbN</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NbN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-21_58_24/NbN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.005878789845947235</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ni/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_16_09/Ni/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.001554625508547957</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Sb2Te3</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sb2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_16_59/Sb2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.006893128049059416</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SiO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_19_40/SiO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.2834066666836649</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SnSe</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SnSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_22_49/SnSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.07795356886573784</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Sr2RuO4</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sr2RuO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_26_38/Sr2RuO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.007235617067140766</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TePb/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_29_07/TePb/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.00915156491734501</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ti/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_32_25/Ti/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0006284199894252312</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>TiC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiC/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_30_23/TiC/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>5.564911547960893e-05</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>TiPbO3</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiPbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_31_56/TiPbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.001185047081731003</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek-V3.2</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Zn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_deepseek-ai/DeepSeek-V3.2-22_35_25/Zn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.002533988950278988</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Al/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_37_40/Al/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.00218945086010734</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>AlN</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/AlN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_35_49/AlN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.006436079360461098</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Au/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_39_40/Au/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>5.478212211909722e-05</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_41_26/BN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.0001710886363886595</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>BaFeO3</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaFeO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_39_52/BaFeO3/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>BaTiO3</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaTiO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_40_11/BaTiO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.00289308718435707</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Bi2Te3</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Bi2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_40_29/Bi2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.01447541379427334</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaCO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_42_41/CaCO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.04040807648938955</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>CaF2</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaF2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_43_00/CaF2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0008008146310858256</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>CoSb3</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CoSb3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_43_44/CoSb3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.004052164062167007</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cr/relax_cr35_reference_rerun_20260625/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_43_47/Cr/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cu/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_44_03/Cu/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.0009486960004225254</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Fe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_47_47/Fe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.001464153083390257</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>FeS2</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeS2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_45_20/FeS2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.009626331802052955</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>FeSe</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_45_35/FeSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.002560599671570589</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Li10Ge(PS6)2</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li10Ge(PS6)2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>missing run structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Li2S</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li2S/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_48_48/Li2S/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.002979002635207655</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Li4Ti5O12</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li4Ti5O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_51_05/Li4Ti5O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.01450867711196074</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Li7La3Zr2O12</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li7La3Zr2O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_58_26/Li7La3Zr2O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.1073273496314046</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>LiCoO2</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiCoO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_58_58/LiCoO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.004822405892536942</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>LiFeAs</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFeAs/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-22_59_00/LiFeAs/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>LiFePO4</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFePO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_01_01/LiFePO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.01975506769471053</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>LiMn2O4</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiMn2O4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_11_13/LiMn2O4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.01357072507847592</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>LiNbO3</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiNbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_18_26/LiNbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.03906814858296064</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Mg/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_50_06/Mg/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.006848893359321939</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>MgB2</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgB2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_34_34/MgB2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0008044383817787275</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgO/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_36_56/MgO/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.0004177368194745261</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NaCl/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_10/relax_gemini-3-pro-preview-23_50_27/NaCl/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.003282824004307226</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Nb3Sn</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Nb3Sn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-00_02_17/Nb3Sn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.003242380704391078</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>NbN</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NbN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-00_03_18/NbN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.004428512457209291</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ni/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-00_11_32/Ni/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Sb2Te3</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sb2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-00_12_47/Sb2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.02264749493946324</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SiO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-00_22_22/SiO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.106834438779738</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SnSe</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SnSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-00_42_25/SnSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.07193074954481446</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sr2RuO4</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sr2RuO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-01_01_15/Sr2RuO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.01033762656259347</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TePb/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-01_04_35/TePb/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.01030790234950421</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ti/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-01_15_43/Ti/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.0005705197960789284</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>TiC</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiC/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-01_07_59/TiC/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.0001113262657198343</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>TiPbO3</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiPbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-01_09_11/TiPbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.001065732384834569</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Gemini-3.1-pro</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Zn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gemini-3-pro-preview-01_26_44/Zn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.002777855529972708</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Al/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_35_22/Al/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.003695146170641203</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>AlN</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/AlN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_34_24/AlN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.03794908910519493</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Au/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_35_52/Au/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.01487157142122967</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_40_58/BN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.03268839892435865</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>BaFeO3</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaFeO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_36_37/BaFeO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.01403336844477177</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>BaTiO3</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaTiO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_38_47/BaTiO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.01848166853434164</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Bi2Te3</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Bi2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_39_34/Bi2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.07763202996618425</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaCO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_41_27/CaCO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.03326000343179441</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CaF2</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaF2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_43_26/CaF2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.05254916328949335</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CoSb3</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CoSb3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_44_14/CoSb3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.007370943702858846</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cr/relax_cr35_reference_rerun_20260625/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_47_33/Cr/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cu/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_47_39/Cu/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0080645863756102</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Fe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_49_53/Fe/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>FeS2</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeS2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_48_04/FeS2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0.02031178488436479</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>FeSe</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_48_53/FeSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.04874525527425488</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Li10Ge(PS6)2</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li10Ge(PS6)2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>missing run structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Li2S</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li2S/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_52_29/Li2S/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.002856582700804524</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Li4Ti5O12</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li4Ti5O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_52_40/Li4Ti5O12/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Li7La3Zr2O12</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li7La3Zr2O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_54_09/Li7La3Zr2O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.1070310183643938</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>LiCoO2</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiCoO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_55_24/LiCoO2/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>LiFeAs</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFeAs/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_56_44/LiFeAs/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>LiFePO4</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFePO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_58_29/LiFePO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0.03422207934179338</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>LiMn2O4</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiMn2O4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-01_59_33/LiMn2O4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.05426383160370985</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>LiNbO3</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiNbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_11_03/LiNbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0.03485105550938997</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Mg/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_23_34/Mg/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.004955035961657632</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>MgB2</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgB2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_20_19/MgB2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.001062571010052342</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgO/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_22_57/MgO/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0.0004041762184044434</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NaCl/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_26_04/NaCl/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0.002619354852309142</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Nb3Sn</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Nb3Sn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_38_55/Nb3Sn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0.003114367227437251</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>NbN</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NbN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_42_57/NbN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0.005208558743679301</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ni/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_46_36/Ni/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Sb2Te3</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sb2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-02_48_37/Sb2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0.02067745752264426</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SiO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_03_20/SiO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0.2546249725939665</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SnSe</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SnSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_13_23/SnSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.07796723508920651</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Sr2RuO4</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sr2RuO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_29_06/Sr2RuO4/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TePb/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_30_48/TePb/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0.008580210575305744</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ti/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_57_01/Ti/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0.0007104329235682016</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>TiC</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiC/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_54_22/TiC/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.0001457823188309226</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>TiPbO3</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiPbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-03_56_42/TiPbO3/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GPT-5.2</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Zn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_gpt-5.2-2025-12-11-04_05_28/Zn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0.002524706870902941</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Al/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-04_12_19/Al/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0.002174726209140115</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>AlN</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/AlN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-04_09_40/AlN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0.006491999669041014</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Au/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-04_13_46/Au/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0.0006543974189220024</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_13_05/BN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0.0001501264636365031</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>BaFeO3</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaFeO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-04_24_06/BaFeO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.005078865331118045</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>BaTiO3</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaTiO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-04_24_55/BaTiO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0.002754618340271681</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Bi2Te3</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Bi2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-04_28_31/Bi2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0.01691640872737636</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaCO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_14_38/CaCO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.04065776602926259</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>CaF2</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaF2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_19_08/CaF2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.001395220923108696</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>CoSb3</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CoSb3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_26_00/CoSb3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0.003680410554974086</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cr/relax_cr35_reference_rerun_20260625/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>missing run structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cu/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_32_39/Cu/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.0007490817609659112</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Fe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_53_00/Fe/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>FeS2</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeS2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_49_59/FeS2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.009916564645328668</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>FeSe</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-05_52_29/FeSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0.05025519965831777</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Li10Ge(PS6)2</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li10Ge(PS6)2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>missing run structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Li2S</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li2S/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-06_09_17/Li2S/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0.003096635491590901</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Li4Ti5O12</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li4Ti5O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-06_38_06/Li4Ti5O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0.01901632038166249</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Li7La3Zr2O12</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li7La3Zr2O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-06_38_13/Li7La3Zr2O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0.05716463819641743</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>LiCoO2</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiCoO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-06_57_43/LiCoO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0.004843795482063104</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>LiFeAs</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFeAs/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-07_19_19/LiFeAs/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0.01738283852758784</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>LiFePO4</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFePO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-07_47_00/LiFePO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0.02066165831263111</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>LiMn2O4</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiMn2O4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-07_52_48/LiMn2O4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0.01356975769464243</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>LiNbO3</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiNbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-08_34_30/LiNbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0.04059187529995337</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Mg/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-08_56_30/Mg/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0.007150569237561343</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>MgB2</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgB2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-08_50_26/MgB2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0.001063408982777002</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgO/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-08_53_24/MgO/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0.0005764371125110992</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NaCl/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_02_08/NaCl/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0.002394179396228564</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Nb3Sn</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Nb3Sn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_04_16/Nb3Sn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>0.003687846603783309</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>NbN</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NbN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_06_38/NbN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>0.00517070010251581</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ni/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_12_54/Ni/vasprun.xml</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>run error: IndexError</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Sb2Te3</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sb2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_13_19/Sb2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>0.02241601623254694</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SiO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_16_03/SiO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0.09289816927010713</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SnSe</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SnSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_21_13/SnSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>0.07628345129924285</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Sr2RuO4</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sr2RuO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_38_32/Sr2RuO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>0.009923374679300831</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TePb/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-09_49_36/TePb/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0.0098295961029743</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ti/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-10_40_12/Ti/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0.0006202745787195522</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>TiC</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiC/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-10_28_09/TiC/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0.0001940706478373686</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>TiPbO3</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiPbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-10_34_27/TiPbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0.001718354792327636</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Qwen3.5-397B</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Zn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>VaspAgent_with_Benchmark/runs/2026_03_11/relax_qwen3.5-397b-a17b-11_10_07/Zn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>0.002569609534474334</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Al/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Al/Al_relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>0.005010466362264667</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>AlN</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/AlN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_AlN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>0.006781066515118519</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Au</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Au/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Au/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>0.0007433407455345569</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_BN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>0.0002527298345290329</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>BaFeO3</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaFeO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_BaFeO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>0.001636226977935028</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>BaTiO3</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/BaTiO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_BaTiO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>0.00516929248363214</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Bi2Te3</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Bi2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Bi2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>0.02696700997074768</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaCO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_CaCO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>0.04060012340417907</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>CaF2</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CaF2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_CaF2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>0.001215635484737187</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>CoSb3</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/CoSb3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_CoSb3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>0.002831342229241778</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Cr</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cr/relax_cr35_reference_rerun_20260625/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_Cr/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>0.006793827931441157</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Cu/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Cu/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>0.0002916568192892844</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Fe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Fe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>0.001107605950592388</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>FeS2</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeS2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_FeS2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>0.008869884269286012</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>FeSe</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/FeSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_FeSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>0.00296297629074598</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Li10Ge(PS6)2</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li10Ge(PS6)2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Li10Ge(PS6)2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>0.1061252169227853</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Li2S</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li2S/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Li2S/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>0.003338437969802597</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Li4Ti5O12</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li4Ti5O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_Li4Ti5O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>0.01725523138912591</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Li7La3Zr2O12</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Li7La3Zr2O12/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Li7La3Zr2O12/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>0.1068396079697189</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>LiCoO2</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiCoO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_LiCoO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>0.003668357717612855</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>LiFeAs</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFeAs/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_LiFeAs/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>0.01815159437277534</v>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>LiFePO4</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiFePO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_LiFePO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>0.01461188746495736</v>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>LiMn2O4</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiMn2O4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_LiMn2O4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>0.04789841258540362</v>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>LiNbO3</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/LiNbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_LiNbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>0.03351610815199555</v>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Mg</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Mg/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Mg/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>0.003480764433610758</v>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>MgB2</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgB2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_MgB2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>0.002226702117341248</v>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>MgO</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/MgO/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_MgO/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>0.0006375832929175597</v>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NaCl/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_NaCl/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>0.00324451541495141</v>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Nb3Sn</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Nb3Sn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Nb3Sn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>0.004783404203116778</v>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>NbN</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/NbN/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_NbN/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>0.006427962652613512</v>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ni/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Ni/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>0.0009001468876979925</v>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Sb2Te3</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sb2Te3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Sb2Te3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>0.02239484384306256</v>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>SiO2</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SiO2/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_SiO2/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>0.2601268953420929</v>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>SnSe</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/SnSe/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_SnSe/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>0.07804890777312104</v>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Sr2RuO4</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Sr2RuO4/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Sr2RuO4/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>0.009982488182287733</v>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>TePb</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TePb/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_TePb/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>0.006869786304625283</v>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Ti/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Ti/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>0.0005990842914616618</v>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>TiC</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiC/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_TiC/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>0.001294122021800792</v>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>TiPbO3</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/TiPbO3/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rxpv_TiPbO3/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>0.007188110101954133</v>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>VASP Agent</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Zn</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>vasp_benchmark_old/relax/Zn/relax/CONTCAR</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>newvaspagent/runs/rx_Zn/CONTCAR</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>0.001189486642385347</v>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15485,7 +21436,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26T12:09:36</t>
+          <t>2026-06-27T23:31:26</t>
         </is>
       </c>
     </row>
@@ -15605,7 +21556,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RMSD_vs_expert is copied from the previous workbook, not recomputed in this environment.</t>
+          <t>RMSD_vs_expert is recomputed from current final structures using pymatgen StructureMatcher(angle_tol=30); CONTCAR is preferred, with vasprun.xml final_structure as fallback.</t>
         </is>
       </c>
     </row>
